--- a/AgriCast360/AgriCast360_V2/Market.xlsx
+++ b/AgriCast360/AgriCast360_V2/Market.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUDA_Experiments\Git_HUB\AgriCast360\Script\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CUDA_Experiments\Git_HUB\Machine-Learning\AgriCast360\AgriCast360_V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD2B800-6FD6-4FC7-9392-83C226098BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F49C0E-A93B-4C42-BEE5-462E7D554964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Bardoli</t>
   </si>
@@ -129,15 +129,6 @@
     <t>Amreli</t>
   </si>
   <si>
-    <t>Ahmedabad</t>
-  </si>
-  <si>
-    <t>Ahmedabad(Chimanbhai Patal Market Vasana)</t>
-  </si>
-  <si>
-    <t>Ahmedabad(Rajnagar sub yard)</t>
-  </si>
-  <si>
     <t>Bavla</t>
   </si>
   <si>
@@ -154,6 +145,9 @@
   </si>
   <si>
     <t>Viramgam</t>
+  </si>
+  <si>
+    <t>Ahmedabad (Vasana)</t>
   </si>
 </sst>
 </file>
@@ -189,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -197,6 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -752,6 +747,12 @@
       <c r="A25" t="s">
         <v>25</v>
       </c>
+      <c r="B25">
+        <v>21.6976857738712</v>
+      </c>
+      <c r="C25">
+        <v>71.517712665659005</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -768,6 +769,12 @@
       <c r="A27" t="s">
         <v>27</v>
       </c>
+      <c r="B27">
+        <v>21.140180675720799</v>
+      </c>
+      <c r="C27">
+        <v>71.254345827115898</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -792,93 +799,84 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30">
+        <v>22.996976855033001</v>
+      </c>
+      <c r="C30">
+        <v>72.536392460074595</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B31">
+        <v>22.830965521422801</v>
+      </c>
+      <c r="C31">
+        <v>72.3579378735662</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B31">
-        <v>22.996976855033001</v>
-      </c>
-      <c r="C31">
-        <v>72.536392460074595</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B32">
+        <v>22.377117706820101</v>
+      </c>
+      <c r="C32">
+        <v>71.978523283421794</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B33">
+        <v>22.7212505077608</v>
+      </c>
+      <c r="C33">
+        <v>72.448905310358995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B33">
-        <v>22.830965521422801</v>
-      </c>
-      <c r="C33">
-        <v>72.3579378735662</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B34">
+        <v>23.282162015159599</v>
+      </c>
+      <c r="C34">
+        <v>71.915345532018506</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B34">
-        <v>22.377117706820101</v>
-      </c>
-      <c r="C34">
-        <v>71.978523283421794</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B35">
+        <v>22.997609695821499</v>
+      </c>
+      <c r="C35">
+        <v>72.381634273951903</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B35">
-        <v>22.7212505077608</v>
-      </c>
-      <c r="C35">
-        <v>72.448905310358995</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
       <c r="B36">
-        <v>23.282162015159599</v>
+        <v>23.125945592319901</v>
       </c>
       <c r="C36">
-        <v>71.915345532018506</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37">
-        <v>22.997609695821499</v>
-      </c>
-      <c r="C37">
-        <v>72.381634273951903</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38">
-        <v>23.125945592319901</v>
-      </c>
-      <c r="C38">
         <v>72.045712191155303</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>